--- a/output/full_scan/batch_seq8_2026-06-11.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-11.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7788</v>
+        <v>8021</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>816.4202670741666</v>
+        <v>1047.247624635017</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>271</v>
+        <v>570</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.7902448236902</v>
+        <v>68.47623368395364</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>37.77344502461035</v>
+        <v>17.14035705665089</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.642026707416666</v>
+        <v>3.7247624635017</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7.069931094318344</v>
+        <v>10.1402459526423</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7722</v>
+        <v>7788</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>767.494295533032</v>
+        <v>1036.687293744848</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>370.5</v>
+        <v>271</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>77.57271624816208</v>
+        <v>75.79024445281718</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>36.44208103885924</v>
+        <v>37.77344496101008</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.749429553303194</v>
+        <v>2.66872937448481</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>12.23948790680654</v>
+        <v>7.069931124273079</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8042</v>
+        <v>7749</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>750</v>
+        <v>1023.809304747632</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>155</v>
+        <v>508</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.13009903440584</v>
+        <v>54.83245869609247</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.14707141895563</v>
+        <v>25.23007520734715</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8.035585817703913</v>
+        <v>1.880930474763156</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-2.685013614053616</v>
+        <v>-2.093569403160412</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8021</v>
+        <v>6944</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>731.6186402319468</v>
+        <v>973.5062966926348</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>570</v>
+        <v>937</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.4762336842123</v>
+        <v>53.44571971312453</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17.1403570610228</v>
+        <v>11.92251188677361</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.661864023194681</v>
+        <v>1.350629669263497</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>10.14024595262322</v>
+        <v>-1.698590148665447</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7749</v>
+        <v>7722</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>713.3674684276626</v>
+        <v>969.5990624675268</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>508</v>
+        <v>370.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>54.83245869609247</v>
+        <v>77.57271605575164</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.23007520734715</v>
+        <v>36.44208106891698</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.836746842766263</v>
+        <v>3.959906246752697</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.093569403160412</v>
+        <v>12.23948790737894</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8043</v>
+        <v>8042</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>668.1141549069253</v>
+        <v>920</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>191.5</v>
+        <v>155</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>74.99423441943556</v>
+        <v>65.13009901930027</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>43.10499554696713</v>
+        <v>40.14707143679056</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.811415490692522</v>
+        <v>8.035585817703913</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.926329022110636</v>
+        <v>-2.685013614053616</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8028</v>
+        <v>6996</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>656.9153805292831</v>
+        <v>903.9581702058454</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>304</v>
+        <v>199</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>53.20502586769112</v>
+        <v>57.61352740222971</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46.01982991297971</v>
+        <v>30.9385800717931</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6915380529283093</v>
+        <v>0.8958170205845321</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-5.258427769325323</v>
+        <v>0.3428674489940637</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8016</v>
+        <v>8043</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>655.302663339713</v>
+        <v>868.1141549069253</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>286.5</v>
+        <v>191.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>52.93168835762555</v>
+        <v>74.99423440591065</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>54.01360363543104</v>
+        <v>43.10499555489157</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5302663339712993</v>
+        <v>1.811415490692522</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-4.336028343265221</v>
+        <v>4.926329022263268</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7827</v>
+        <v>8016</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>650.3950033780078</v>
+        <v>850.4443709398828</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>157</v>
+        <v>286.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.06152545454997</v>
+        <v>52.93168830932267</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.34110108768463</v>
+        <v>54.01360363269078</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5395003378007797</v>
+        <v>0.544437093988284</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.153883317906752</v>
+        <v>-4.336028342979059</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7769</v>
+        <v>6870</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>649.2952021498985</v>
+        <v>844.7776495995757</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7055</v>
+        <v>300</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>52.8218056257514</v>
+        <v>65.16621835370705</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.31196680829358</v>
+        <v>34.60593692133779</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9295202149898542</v>
+        <v>0.9777649599575788</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-181.6635394767065</v>
+        <v>3.070901758759923</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6870</v>
+        <v>8044</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>644.7776495995757</v>
+        <v>834.7276333787445</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>300</v>
+        <v>29.55</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.16621840304514</v>
+        <v>56.18105225834551</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.6059369147215</v>
+        <v>34.01898286547173</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9777649599575788</v>
+        <v>0.4727633378744431</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3.070901758950701</v>
+        <v>-0.0176667782585633</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6922</v>
+        <v>6916</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>641.9152904185345</v>
+        <v>800.7059600996927</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>186.5</v>
+        <v>20.35</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>49.07829475456398</v>
+        <v>59.53965911758485</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.4123368513559</v>
+        <v>26.0284384509411</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6915290418534495</v>
+        <v>1.070596009969266</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.262420649648552</v>
+        <v>0.2305437571919253</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6944</v>
+        <v>7827</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>627.9951498987157</v>
+        <v>790.4259354776226</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>937</v>
+        <v>157</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>53.44571975400992</v>
+        <v>59.06152545454997</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11.92251188677361</v>
+        <v>21.34110108768463</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.299514989871567</v>
+        <v>0.5425935477622617</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.698590148474699</v>
+        <v>1.153883317906752</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8044</v>
+        <v>6957</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>619.7276333787445</v>
+        <v>789.39205357605</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>29.55</v>
+        <v>185.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.18105261063658</v>
+        <v>64.87612850590679</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>34.01898256660835</v>
+        <v>31.17619684247886</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4727633378744431</v>
+        <v>0.939205357605004</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.0176667789358846</v>
+        <v>1.805861635445378</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8039</v>
+        <v>6922</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>599.4772099925106</v>
+        <v>781.9152904185345</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>136</v>
+        <v>186.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46.83452480209355</v>
+        <v>49.07829467976738</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27.22779811619139</v>
+        <v>28.41233694884798</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.44772099925105</v>
+        <v>0.6915290418534495</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-2.688858910534076</v>
+        <v>-1.262420649553142</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8040</v>
+        <v>7769</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>589.8670764581871</v>
+        <v>765.1067704790686</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>96.5</v>
+        <v>7055</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>50.72189669769014</v>
+        <v>52.82180561724542</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>39.71793374653623</v>
+        <v>31.31196667865278</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4867076458187004</v>
+        <v>1.010677047906864</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-3.254281095780946</v>
+        <v>-181.6635394721276</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6957</v>
+        <v>6997</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>584.29506493134</v>
+        <v>759.6196110726573</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>185.5</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>64.87612849498584</v>
+        <v>55.05344717741388</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.17619685992673</v>
+        <v>6.811498421550465</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.929506493134001</v>
+        <v>0.9619611072657366</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.805861635826958</v>
+        <v>0.2882944523590665</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6902</v>
+        <v>8039</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>582.1912107959862</v>
+        <v>759.5258965271756</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.84439884434506</v>
+        <v>46.83452479731966</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>42.22102708171086</v>
+        <v>27.22779812803577</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7191210795986195</v>
+        <v>0.4525896527175685</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-1.511513080316176</v>
+        <v>-2.688858910543632</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8032</v>
+        <v>7734</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>581.8882054404753</v>
+        <v>731.7687903570494</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>43.25</v>
+        <v>3080</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>50.82991204278289</v>
+        <v>43.8162675073179</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.38903533910112</v>
+        <v>27.39023275093933</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6888205440475362</v>
+        <v>1.17687903570494</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.4223219479064524</v>
+        <v>-68.58938301775792</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6907</v>
+        <v>7786</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>575.9643114485502</v>
+        <v>725.8833622788246</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>52.57339631464885</v>
+        <v>57.19104633992763</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.01328445123506</v>
+        <v>18.4144801404135</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.09643114485503</v>
+        <v>2.588336227882462</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,11 +1577,11 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.016543127499814</v>
+        <v>1.547932485510544</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>570.295358649789</v>
+        <v>710.5112523253708</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>17.25</v>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>48.42604923769806</v>
+        <v>48.4260491263855</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.0819235812268</v>
+        <v>22.08192370978685</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.529535864978903</v>
+        <v>1.551125232537083</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.028192803230187</v>
+        <v>0.0281928032969649</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6996</v>
+        <v>6899</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>568.9581702058454</v>
+        <v>708.244771958698</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>199</v>
+        <v>61.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.61352752587845</v>
+        <v>52.73336147852234</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.93858010652535</v>
+        <v>25.82588626442202</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8958170205845321</v>
+        <v>0.3244771958698069</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3428674482308684</v>
+        <v>-0.5667165312266631</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6997</v>
+        <v>6949</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>559.6196110726573</v>
+        <v>689.5404972502871</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>78</v>
+        <v>704</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.05344617877905</v>
+        <v>54.38751903220781</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6.811498420396996</v>
+        <v>20.01660192850835</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9619611072657366</v>
+        <v>1.954049725028714</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2882944523590665</v>
+        <v>7.319092347117744</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7721</v>
+        <v>8028</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>539.9714004786155</v>
+        <v>687.0763973095912</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>75.8</v>
+        <v>304</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.27470645117016</v>
+        <v>53.2050258480724</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14.31643604177643</v>
+        <v>46.01982990408946</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4971400478615492</v>
+        <v>0.7076397309591284</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0595541361427857</v>
+        <v>-5.258427769229904</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6899</v>
+        <v>6901</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>538.244771958698</v>
+        <v>685.0083506543056</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>61.6</v>
+        <v>16.05</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.7333615205046</v>
+        <v>68.13957656159641</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>25.82588623729582</v>
+        <v>27.78084219294397</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3244771958698069</v>
+        <v>1.000835065430559</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.5667165313602192</v>
+        <v>0.3647410938402713</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7712</v>
+        <v>7721</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>527.41949685765</v>
+        <v>680.0293755370953</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>138.5</v>
+        <v>75.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>43.51073760043563</v>
+        <v>49.2747064242037</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.39209655810163</v>
+        <v>14.31643608001581</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2419496857649953</v>
+        <v>0.5029375537095389</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-4.562208283134929</v>
+        <v>-0.0595541360664668</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7786</v>
+        <v>8032</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>525.5640791912901</v>
+        <v>671.8882054404754</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>130</v>
+        <v>43.25</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.19104643387153</v>
+        <v>50.8299119636413</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18.4144801404135</v>
+        <v>29.38903533643561</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.556407919129019</v>
+        <v>0.6888205440475362</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.547932485605961</v>
+        <v>-0.422321947992315</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6906</v>
+        <v>7747</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>517.3594275601292</v>
+        <v>662.2884314589653</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.71121173744299</v>
+        <v>51.72221649444457</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>37.43201449408225</v>
+        <v>9.736899055754858</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7359427560129261</v>
+        <v>1.728843145896525</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.436224471223003</v>
+        <v>1.046875278544868</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6861</v>
+        <v>6895</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>511.1370470241893</v>
+        <v>626.665328977664</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>303.5</v>
+        <v>169</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>38.74527620898534</v>
+        <v>58.98068217725965</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>36.73620596022189</v>
+        <v>19.678270252225</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6137047024189231</v>
+        <v>0.6665328977663962</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-19.36274890942974</v>
+        <v>2.956962591821017</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6916</v>
+        <v>6859</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>505.5453128604355</v>
+        <v>609.7688837499222</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>20.35</v>
+        <v>125.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.53965910508905</v>
+        <v>51.74279130412678</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.02843862599888</v>
+        <v>24.2179349834215</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.05453128604355</v>
+        <v>0.4768883749922168</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2305437567626406</v>
+        <v>-0.1363722057410563</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6894</v>
+        <v>6855</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>505.5251308595102</v>
+        <v>607.3338406900051</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>343</v>
+        <v>126.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>43.55065929910474</v>
+        <v>56.68658556669776</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>28.306144486821</v>
+        <v>14.80496924761991</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5525130859510233</v>
+        <v>0.2333840690005073</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-5.462360264294983</v>
+        <v>0.6844518901069412</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7734</v>
+        <v>6965</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>496.7687903570494</v>
+        <v>596.1685580646144</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3080</v>
+        <v>81.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>43.81626751735378</v>
+        <v>55.42262730785433</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.39023271833089</v>
+        <v>22.05547771184095</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.17687903570494</v>
+        <v>0.6168558064614411</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-68.58938301546834</v>
+        <v>0.6466364857613528</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6859</v>
+        <v>8040</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>494.7688837499222</v>
+        <v>589.8670764581871</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>125.5</v>
+        <v>96.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.74279136624685</v>
+        <v>50.72189665931737</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.217934908782</v>
+        <v>39.71793377757636</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4768883749922168</v>
+        <v>0.4867076458187004</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.136372205264065</v>
+        <v>-3.254281095647394</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7747</v>
+        <v>6902</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>492.2884314589653</v>
+        <v>582.3234451261897</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.72221651192571</v>
+        <v>52.84439776212625</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>9.736898975007648</v>
+        <v>42.22102710538532</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.728843145896525</v>
+        <v>0.7323445126189729</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.046875278449464</v>
+        <v>-1.511513080029989</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6949</v>
+        <v>6907</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>489.3083507410183</v>
+        <v>575.9643114485502</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>704</v>
+        <v>136</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.3875190406485</v>
+        <v>52.57339631464885</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.01660192850835</v>
+        <v>30.01328445123506</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.93083507410183</v>
+        <v>1.09643114485503</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>7.319092347117744</v>
+        <v>1.016543127499814</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6901</v>
+        <v>7714</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>484.98449433766</v>
+        <v>550.8405951645454</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>16.05</v>
+        <v>127</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>68.13957678585626</v>
+        <v>48.26866669626796</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.78084218402944</v>
+        <v>26.44904116675215</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.998449433765996</v>
+        <v>0.5840595164545381</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.3647410938402713</v>
+        <v>1.196061621612725</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6855</v>
+        <v>8038</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>467.333840690005</v>
+        <v>546.1254420966256</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>126.5</v>
+        <v>41.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.68658553824369</v>
+        <v>50.65943812879336</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.80496924696526</v>
+        <v>10.24713737206402</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2333840690005073</v>
+        <v>1.112544209662568</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.6844518907747252</v>
+        <v>0.0566495704995972</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6934</v>
+        <v>7717</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>459.1661719337495</v>
+        <v>528.6313438027371</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>70.7</v>
+        <v>599</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>39.35781193076448</v>
+        <v>43.0070709265997</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30.86462649568248</v>
+        <v>15.12081109696486</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4166171933749534</v>
+        <v>2.863134380273704</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0034745964195699</v>
+        <v>-2.414287471280595</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6924</v>
+        <v>7744</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>458.9062544621073</v>
+        <v>527.753069470741</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>121</v>
+        <v>501</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>38.97381329337379</v>
+        <v>50.92501301882968</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>47.46948610125219</v>
+        <v>16.46363977611507</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.390625446210732</v>
+        <v>0.7753069470741023</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-8.225088180364384</v>
+        <v>-1.37368284395988</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8038</v>
+        <v>7712</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>431.1254420966257</v>
+        <v>527.41949685765</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>41.7</v>
+        <v>138.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.65943812879336</v>
+        <v>43.5107375643777</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10.24713738965749</v>
+        <v>23.39209651129729</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.112544209662568</v>
+        <v>0.2419496857649953</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0566495705949979</v>
+        <v>-4.562208283421128</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7750</v>
+        <v>7728</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>415.9975395258863</v>
+        <v>525.7530573577019</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2090</v>
+        <v>714</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>40.40010281049553</v>
+        <v>46.33940275328286</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.51575657435217</v>
+        <v>9.836305335334226</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5997539525886262</v>
+        <v>1.075305735770191</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-55.11091570061711</v>
+        <v>-2.44770508078285</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7728</v>
+        <v>6861</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>410.7530573577019</v>
+        <v>521.3994190713267</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>714</v>
+        <v>303.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46.33940284733372</v>
+        <v>38.74527620394156</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9.836305282075612</v>
+        <v>36.73620599218052</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.075305735770191</v>
+        <v>0.6399419071326832</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.447705085838829</v>
+        <v>-19.36274890937252</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7792</v>
+        <v>6906</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>409.7480929460494</v>
+        <v>517.507120120153</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>37.72136301123236</v>
+        <v>51.71121171642124</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.62352157048443</v>
+        <v>37.4320153788175</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4748092946049444</v>
+        <v>0.7507120120152992</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.215239829975264</v>
+        <v>-1.436224471413794</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7711</v>
+        <v>7821</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>391.3292694198014</v>
+        <v>511.9463602179281</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>357.5</v>
+        <v>44.65</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.92712562866297</v>
+        <v>44.38604057038226</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.90260130513866</v>
+        <v>22.43666244980372</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6329269419801371</v>
+        <v>0.694636021792815</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-6.321612930205093</v>
+        <v>0.4128725386973042</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7556</v>
+        <v>6862</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>391.0944972212394</v>
+        <v>506.5770810185787</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.55368771604849</v>
+        <v>49.56696134072041</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.89585074254761</v>
+        <v>23.25527539562316</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6094497221239356</v>
+        <v>1.157708101857871</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.172100960686666</v>
+        <v>-0.5501704162867007</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6965</v>
+        <v>7750</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>386.095738879749</v>
+        <v>506.4797812132069</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>81.8</v>
+        <v>2090</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.42262780998053</v>
+        <v>40.40010280482422</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.05547773304857</v>
+        <v>25.51575658143883</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6095738879748961</v>
+        <v>0.6479781213206922</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.6466364857613528</v>
+        <v>-55.11091570033085</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7714</v>
+        <v>7556</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>380.8405951645454</v>
+        <v>506.0944972212394</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.26866672126194</v>
+        <v>46.55368768459897</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.44904115216461</v>
+        <v>18.8958507616351</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5840595164545381</v>
+        <v>0.6094497221239356</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.1960616219943</v>
+        <v>-2.172100960495897</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7821</v>
+        <v>6894</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>371.7949546512698</v>
+        <v>505.5251308595102</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>44.65</v>
+        <v>343</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.38604056269988</v>
+        <v>43.55065926997758</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.43666245247851</v>
+        <v>28.30614462646601</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6794954651269831</v>
+        <v>0.5525130859510233</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.4128725390884358</v>
+        <v>-5.462360264676574</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6951</v>
+        <v>6934</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>369.8298050096264</v>
+        <v>504.2781550248267</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>79.5</v>
+        <v>70.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>42.4891506821736</v>
+        <v>39.35780976456039</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>28.1756196091473</v>
+        <v>30.86462733310868</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.98298050096264</v>
+        <v>0.4278155024826595</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1078668991971054</v>
+        <v>0.0034746074093257</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6925</v>
+        <v>7631</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>360.8899715892578</v>
+        <v>488.8932640982946</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>127</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.36977003643234</v>
+        <v>52.06986241253114</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.19407397678747</v>
+        <v>11.76482519176278</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5889971589257736</v>
+        <v>2.389326409829462</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.126138483830135</v>
+        <v>1.34736443149249</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6895</v>
+        <v>7705</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>351.665328977664</v>
+        <v>487.9655953420253</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>58.98068218432579</v>
+        <v>41.00022519999109</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.67827025767214</v>
+        <v>21.65207093187576</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6665328977663962</v>
+        <v>0.7965595342025245</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.956962592488795</v>
+        <v>0.1298045578295735</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7730</v>
+        <v>6951</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>350.0887335439338</v>
+        <v>485.5819060575626</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>179</v>
+        <v>79.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>41.19932398324774</v>
+        <v>42.4891506776134</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.86682453416846</v>
+        <v>28.17561962298972</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5088733543933731</v>
+        <v>2.058190605756259</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-5.013928498792336</v>
+        <v>-0.1078668992543412</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7705</v>
+        <v>6925</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>347.7855929651021</v>
+        <v>475.8899715892578</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>31</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>41.00022515167069</v>
+        <v>48.36977004699678</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.65207091713013</v>
+        <v>29.19407397345609</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7785592965102104</v>
+        <v>0.5889971589257736</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1298045579249725</v>
+        <v>1.126138483772906</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6903</v>
+        <v>8048</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>342.667044181532</v>
+        <v>473.9776308805812</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>368</v>
+        <v>62.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.15183433939219</v>
+        <v>51.0652844179191</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.41056599575898</v>
+        <v>16.8815401116405</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7667044181532042</v>
+        <v>0.8977630880581136</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-4.915918282118614</v>
+        <v>-0.0735841509800849</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7740</v>
+        <v>6955</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>342.3864236569345</v>
+        <v>470.8902503091055</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.40760999224919</v>
+        <v>49.1088418974839</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11.21553898876863</v>
+        <v>4.598155735034027</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2386423656934493</v>
+        <v>0.5890250309105478</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.3528463450054131</v>
+        <v>0.6265114386919676</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7805</v>
+        <v>8047</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>339.0321750214874</v>
+        <v>470.6351113450849</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>688</v>
+        <v>52.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>34.92334605979755</v>
+        <v>54.89264303096658</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>31.00518408563407</v>
+        <v>8.669548011935268</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9032175021487384</v>
+        <v>0.5635111345084853</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-11.61102755047325</v>
+        <v>1.224068332490716</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7717</v>
+        <v>7780</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>338.631343802737</v>
+        <v>467.9111847103578</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>599</v>
+        <v>18.4</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>43.0070709265997</v>
+        <v>48.24802110431062</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.12081109696486</v>
+        <v>22.21457288718129</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2.863134380273704</v>
+        <v>0.7911184710357734</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-2.414287471280595</v>
+        <v>0.2014257830497384</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6862</v>
+        <v>7730</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>336.3906431614462</v>
+        <v>465.1366612450067</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>49.56696139597355</v>
+        <v>41.19932394461382</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.25527541484903</v>
+        <v>21.86682456706652</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.139064316144615</v>
+        <v>0.5136661245006661</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.5501704170498822</v>
+        <v>-5.013928498639699</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6933</v>
+        <v>7711</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>335.511100995841</v>
+        <v>461.5777117646653</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>148.5</v>
+        <v>357.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.95803778911055</v>
+        <v>43.92712565255087</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.20471896785681</v>
+        <v>18.90260150128667</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5511100995841055</v>
+        <v>0.6577711764665332</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-2.796111073241134</v>
+        <v>-6.321612931922217</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6955</v>
+        <v>7704</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>335.3220647482397</v>
+        <v>453.8456395436101</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>139</v>
+        <v>61.1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.10884190178272</v>
+        <v>48.77990254095575</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4.598155931506175</v>
+        <v>15.31219083705643</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5322064748239727</v>
+        <v>0.3845639543610021</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.6265114388827728</v>
+        <v>-0.533211898385509</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8048</v>
+        <v>6931</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>333.9776308805812</v>
+        <v>445.1905441159018</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>62.8</v>
+        <v>40.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.06528445919943</v>
+        <v>37.69693425901315</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.88154012684484</v>
+        <v>34.77341687730724</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8977630880581136</v>
+        <v>0.519054411590183</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0735841508656052</v>
+        <v>0.3988565086700597</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7768</v>
+        <v>7760</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>331.5739753880476</v>
+        <v>439.0093155454578</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>373.5</v>
+        <v>32</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.59494016453274</v>
+        <v>35.81460421275698</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.62317303380015</v>
+        <v>58.05221544471334</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6573975388047528</v>
+        <v>0.4009315545457729</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.3307348999161407</v>
+        <v>0.0800831322215742</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7822</v>
+        <v>6924</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>328.5977142569999</v>
+        <v>438.9571891483944</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>946</v>
+        <v>121</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>35.73453876855444</v>
+        <v>38.97381330993367</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.65684638314074</v>
+        <v>47.46948632535899</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8597714256999912</v>
+        <v>1.395718914839436</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.66386097889405</v>
+        <v>-8.225088180688731</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7744</v>
+        <v>7803</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>327.753069470741</v>
+        <v>435.4676618360294</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>501</v>
+        <v>22.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.92501302033076</v>
+        <v>37.26291934233446</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.46363977889215</v>
+        <v>23.27500681509369</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7753069470741023</v>
+        <v>0.546766183602939</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.373682844436836</v>
+        <v>0.168602050806462</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7799</v>
+        <v>6952</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>325.2998962748403</v>
+        <v>424.2412618633762</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>334.5</v>
+        <v>36</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.5778244625679</v>
+        <v>38.94814301927928</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>26.90586352634035</v>
+        <v>18.71091090518681</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5299896274840241</v>
+        <v>0.924126186337617</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>4.052847462751267</v>
+        <v>0.005903623494604</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8046</v>
+        <v>7736</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>320.5473243536895</v>
+        <v>422.0375710555805</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>807</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.55623676845087</v>
+        <v>45.1143331266731</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.22225200441999</v>
+        <v>17.74158553619718</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.054732435368953</v>
+        <v>0.2037571055580473</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-10.88532153348099</v>
+        <v>0.1764880260583268</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7704</v>
+        <v>6910</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>313.84563954361</v>
+        <v>417.513360209755</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>61.1</v>
+        <v>28.9</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.77990260135181</v>
+        <v>52.1038601579222</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.31219082448163</v>
+        <v>15.03150206646325</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3845639543610021</v>
+        <v>0.2513360209755018</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.5332118978512892</v>
+        <v>0.1657043340765471</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6885</v>
+        <v>7792</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>308.847088197138</v>
+        <v>409.7480929460494</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>22.95</v>
+        <v>259</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>47.84873478750537</v>
+        <v>37.72136299879082</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26.3422482272588</v>
+        <v>23.62352165796748</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8847088197137987</v>
+        <v>0.4748092946049444</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,11 +4121,11 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2265374332972883</v>
+        <v>-0.2152398296890467</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>308.3454612187269</v>
+        <v>404.0202301347544</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>242.5</v>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.92349684565232</v>
+        <v>45.92349676378681</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>34.75382110205135</v>
+        <v>34.75382112360175</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8345461218726874</v>
+        <v>0.902023013475442</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.71068113615407</v>
+        <v>-1.710681135390915</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6865</v>
+        <v>7768</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>307.7000731101851</v>
+        <v>402.0738722715176</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>27.35</v>
+        <v>373.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.6317303911615</v>
+        <v>43.59494015269132</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>31.71010807213289</v>
+        <v>16.62317303380016</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.270007311018511</v>
+        <v>0.7073872271517597</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1531925114383501</v>
+        <v>-0.3307348999161407</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6931</v>
+        <v>8033</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>305.1211620382225</v>
+        <v>399.772715684985</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>40.6</v>
+        <v>126.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.69693437490697</v>
+        <v>37.5516623438314</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>34.77341687730726</v>
+        <v>8.3198677919075</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5121162038222491</v>
+        <v>0.4772715684984946</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.3988565087082163</v>
+        <v>-0.7433226323208455</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8033</v>
+        <v>7715</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>304.5692245598451</v>
+        <v>394.910068864526</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>126.5</v>
+        <v>27.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>37.55166237583249</v>
+        <v>46.20221497315718</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8.31986778056736</v>
+        <v>20.25824003244431</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4569224559845068</v>
+        <v>0.4910068864525996</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.7433226323971502</v>
+        <v>-0.0194135354486454</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6863</v>
+        <v>6983</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>298.02980362766</v>
+        <v>392.8356491787197</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>94.3</v>
+        <v>349.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>34.76316331319086</v>
+        <v>41.82112223310863</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21.686051210868</v>
+        <v>15.30292989400843</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2.302980362766</v>
+        <v>0.2835649178719681</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.932140156782998</v>
+        <v>-2.241083828465726</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7780</v>
+        <v>7738</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>297.8286072581104</v>
+        <v>391.386969601769</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18.4</v>
+        <v>169</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.24802110431062</v>
+        <v>46.04202223125325</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.21457309097089</v>
+        <v>20.51079850296947</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7828607258110426</v>
+        <v>0.6386969601768998</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2014257842608058</v>
+        <v>0.4657283291759579</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6854</v>
+        <v>7753</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>293.9785270841488</v>
+        <v>366.6254879858642</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>130.5</v>
+        <v>41.6</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>36.32498084087825</v>
+        <v>44.56436690688307</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.05107172289572</v>
+        <v>20.8645952418565</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3978527084148748</v>
+        <v>1.162548798586419</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.493922917440031</v>
+        <v>-0.1876264584240375</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7631</v>
+        <v>6914</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>288.5323725370675</v>
+        <v>362.6400291669162</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>127</v>
+        <v>141.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.06986241979808</v>
+        <v>44.31061141987158</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.76482498334549</v>
+        <v>16.17978507344257</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.353237253706757</v>
+        <v>0.7640029166916241</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.34736443124445</v>
+        <v>0.1704556318931069</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6909</v>
+        <v>6918</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>284.2733598312845</v>
+        <v>358.6123152795816</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>43.7</v>
+        <v>72.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>31.29400366083509</v>
+        <v>44.68979913310429</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.02414429133756</v>
+        <v>9.19537099122816</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9273359831284496</v>
+        <v>0.8612315279581593</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.9218591968580464</v>
+        <v>-0.0251686151841003</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6952</v>
+        <v>8024</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>284.121439529002</v>
+        <v>355.849508348419</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>36</v>
+        <v>12.15</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>38.94814307546813</v>
+        <v>37.54100803108522</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.71091082882509</v>
+        <v>19.63407896318937</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9121439529002032</v>
+        <v>0.5849508348419034</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0059036235136785</v>
+        <v>-0.0255276365167762</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6994</v>
+        <v>6885</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>279.1152796614481</v>
+        <v>353.9132955159873</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>56.3</v>
+        <v>22.95</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>38.84395955054879</v>
+        <v>47.84873473001245</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.93833196374829</v>
+        <v>26.34224823264985</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.411527966144806</v>
+        <v>0.8913295515987325</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0859011756609154</v>
+        <v>0.2265374332972883</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6910</v>
+        <v>7751</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>277.513360209755</v>
+        <v>353.1266698212158</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>28.9</v>
+        <v>1320</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.10386011297926</v>
+        <v>34.7892156001259</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15.03150201473416</v>
+        <v>19.32807463169783</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2513360209755018</v>
+        <v>1.312666982121583</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1657043341719443</v>
+        <v>-31.93166629150227</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6869</v>
+        <v>7842</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>275.4609287892233</v>
+        <v>350.2894960904073</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>78.5</v>
+        <v>106</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39.14948492775826</v>
+        <v>36.53013489590632</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.32320761483806</v>
+        <v>27.10570470271424</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.046092878922324</v>
+        <v>0.5289496090407356</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.300620537438576</v>
+        <v>1.234921009559969</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7810</v>
+        <v>7820</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>273.0729482677893</v>
+        <v>350.2026311535473</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>199.5</v>
+        <v>117</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>36.0556451072209</v>
+        <v>31.65601185854095</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.09523248433192</v>
+        <v>30.93098370745929</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3072948267789377</v>
+        <v>0.5202631153547336</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-3.986966955059721</v>
+        <v>0.3807592052722111</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7791</v>
+        <v>6923</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>273.03978356741</v>
+        <v>350.1651461589825</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>62.7</v>
+        <v>78.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>37.71404691593477</v>
+        <v>46.75364627910683</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>27.45535361583728</v>
+        <v>15.2406804746837</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.303978356741</v>
+        <v>0.5165146158982477</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.3641380678322314</v>
+        <v>0.1748699577349435</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8047</v>
+        <v>7732</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>270.6351113450849</v>
+        <v>346.3838103861813</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>52.3</v>
+        <v>35.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>54.89264303450379</v>
+        <v>50.07747775935297</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8.669548011935269</v>
+        <v>13.68531397553523</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5635111345084853</v>
+        <v>0.138381038618125</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.224068332519338</v>
+        <v>-0.0103886175991033</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7751</v>
+        <v>6903</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>263.1266698212158</v>
+        <v>342.667044181532</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1320</v>
+        <v>368</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>34.7892156001259</v>
+        <v>42.15183433268408</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.32807464475241</v>
+        <v>20.41056602141125</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.312666982121583</v>
+        <v>0.7667044181532042</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-31.93166629064365</v>
+        <v>-4.915918282214053</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6908</v>
+        <v>7740</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>261.200602787171</v>
+        <v>342.4172599769672</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>38.65</v>
+        <v>169</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.15406566888073</v>
+        <v>46.40760993245535</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.04572747131746</v>
+        <v>11.21553903294686</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6200602787170952</v>
+        <v>0.2417259976967214</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1775900668439457</v>
+        <v>-0.3528463450054131</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7795</v>
+        <v>7805</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>259.9299722558832</v>
+        <v>339.0321750214874</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>350</v>
+        <v>688</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.57028090321719</v>
+        <v>34.92334611225819</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.91417365275456</v>
+        <v>31.00518408563407</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9929972255883198</v>
+        <v>0.9032175021487384</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-4.896141820700795</v>
+        <v>-11.61102755505244</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7772</v>
+        <v>6967</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>259.4707691677681</v>
+        <v>338.7311824588314</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>143.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.94647391981658</v>
+        <v>45.04471974510973</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.03314032284102</v>
+        <v>10.42081595065178</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4470769167768164</v>
+        <v>0.8731182458831404</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.8331683743306622</v>
+        <v>-0.1741091913425211</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7803</v>
+        <v>6933</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.4318368380784</v>
+        <v>335.6723527311579</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>22.8</v>
+        <v>148.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.26291952108581</v>
+        <v>39.95803784090955</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>23.27500666443373</v>
+        <v>17.20471888426031</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5431836838078397</v>
+        <v>0.5672352731157876</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1686020506347467</v>
+        <v>-2.796111076580049</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6937</v>
+        <v>7822</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>255.1588087929645</v>
+        <v>330.3620733989072</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>277.5</v>
+        <v>946</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.17190042670667</v>
+        <v>35.73453874898333</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.42591593007394</v>
+        <v>15.65684635791053</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5158808792964539</v>
+        <v>1.036207339890725</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-4.490496844314705</v>
+        <v>-1.663860977367762</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7715</v>
+        <v>6921</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>254.910068864526</v>
+        <v>329.6040861940247</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>27.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>46.20221500018981</v>
+        <v>32.79706591470423</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.25824002790225</v>
+        <v>24.84354042673328</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4910068864525996</v>
+        <v>0.960408619402466</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0194135354009469</v>
+        <v>-0.4498779691759074</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6913</v>
+        <v>6908</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>253.5134362939624</v>
+        <v>326.667697609685</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>123</v>
+        <v>38.65</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.65472770871605</v>
+        <v>44.15406554137578</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.89815958949425</v>
+        <v>11.04572746428226</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3513436293962333</v>
+        <v>0.6667697609684973</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-2.193376990339132</v>
+        <v>0.1775900668439457</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6983</v>
+        <v>8046</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>252.8356491787197</v>
+        <v>320.9804387476201</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>349.5</v>
+        <v>807</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.82112250997548</v>
+        <v>45.5562367632475</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.30292995506659</v>
+        <v>19.2222519595087</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2835649178719681</v>
+        <v>1.098043874762009</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-2.241083829133494</v>
+        <v>-10.88532153338562</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7842</v>
+        <v>6969</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>235.2894960904074</v>
+        <v>317.2948960962768</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>106</v>
+        <v>26.75</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.53013489590632</v>
+        <v>29.85494299255338</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>27.10570470271424</v>
+        <v>20.2815814125898</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5289496090407356</v>
+        <v>0.7294896096276775</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>1.234921009559969</v>
+        <v>-0.081402633455414</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7820</v>
+        <v>6988</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>235.2026311535473</v>
+        <v>314.4803858017941</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>117</v>
+        <v>13.85</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>31.65601185854095</v>
+        <v>31.32453116777963</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>30.93098370745929</v>
+        <v>21.42775614994637</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5202631153547336</v>
+        <v>0.4480385801794063</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3807592052722111</v>
+        <v>-0.2526970793194792</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7823</v>
+        <v>6865</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>231.6138455033423</v>
+        <v>307.7000731101851</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>83.5</v>
+        <v>27.35</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>30.46071759679407</v>
+        <v>49.6317303280773</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>28.18039688687769</v>
+        <v>31.71010850084346</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.1613845503342273</v>
+        <v>0.270007311018511</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-2.479154100771361</v>
+        <v>-0.1531925105034588</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7753</v>
+        <v>6854</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>226.6254879858642</v>
+        <v>299.0572606770485</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>41.6</v>
+        <v>130.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.56436678607928</v>
+        <v>36.32498078877754</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.86459525325867</v>
+        <v>16.05107176689418</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.162548798586419</v>
+        <v>0.4057260677048503</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.187626458290485</v>
+        <v>-2.493922917917012</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7738</v>
+        <v>6863</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>221.386969601769</v>
+        <v>298.9801391911686</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>169</v>
+        <v>94.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.04202220948912</v>
+        <v>34.76316317882791</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.51079839403324</v>
+        <v>21.68605118577941</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6386969601768998</v>
+        <v>2.398013919116856</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.4657283292713403</v>
+        <v>-1.932140156687609</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6918</v>
+        <v>7799</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>218.3480614373385</v>
+        <v>295.5391210567063</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>72.8</v>
+        <v>334.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.68979897250357</v>
+        <v>46.57782437266221</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>9.195370966452098</v>
+        <v>26.90586356299309</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8348061437338462</v>
+        <v>0.5539121056706346</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0251686144209308</v>
+        <v>4.052847462178894</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8024</v>
+        <v>6962</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>215.8495083484191</v>
+        <v>295.1684083103577</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>12.15</v>
+        <v>34.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,49 +5799,49 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.54100783543152</v>
+        <v>42.44523913695505</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>19.63407883376252</v>
+        <v>15.12843586645051</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5849508348419034</v>
+        <v>0.5168408310357736</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0255276363736813</v>
+        <v>-0.549146188379704</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6921</v>
+        <v>7818</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>214.0677746402244</v>
+        <v>292.8845130089638</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>62</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>32.79706591470423</v>
+        <v>24.67139072496535</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>24.84354042673328</v>
+        <v>45.9550437720282</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9067774640224416</v>
+        <v>0.2884513008963799</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.4498779691759074</v>
+        <v>0.9533932541881036</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7736</v>
+        <v>6909</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>211.9690770513915</v>
+        <v>284.324578111548</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>43.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.11433317256945</v>
+        <v>31.29400361740581</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.74158555414276</v>
+        <v>20.02414433199595</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.1969077051391504</v>
+        <v>0.932457811154801</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1764880265353092</v>
+        <v>-0.9218591968198866</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8011</v>
+        <v>6994</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>210.969798270619</v>
+        <v>279.1709519480941</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>17.95</v>
+        <v>56.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.41395341055519</v>
+        <v>38.84395943454499</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.50829996929248</v>
+        <v>19.93833196374829</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5969798270618973</v>
+        <v>0.4170951948094084</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0207903889187042</v>
+        <v>0.0859011754319686</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,18 +5986,18 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6923</v>
+        <v>6869</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>210.160361337205</v>
+        <v>275.6423167782582</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>78.5</v>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.75364629159567</v>
+        <v>39.14948489627311</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.24068040492491</v>
+        <v>17.32320761094944</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5160361337205055</v>
+        <v>1.064231677825816</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.174869957715863</v>
+        <v>-0.3006205382971534</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7760</v>
+        <v>6936</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>208.9929257409985</v>
+        <v>274.629661721891</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>32</v>
+        <v>33.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.81460415549043</v>
+        <v>43.9042694848761</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>58.05221554766601</v>
+        <v>13.53773914577086</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3992925740998495</v>
+        <v>0.462966172189103</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0800831322215742</v>
+        <v>0.0334434391209998</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7818</v>
+        <v>7810</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>207.8238967862688</v>
+        <v>273.0729482677893</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>62</v>
+        <v>199.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>24.67139074415515</v>
+        <v>36.05564510473409</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>45.95504379070401</v>
+        <v>17.095232487224</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2823896786268817</v>
+        <v>0.3072948267789377</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.9533932540927008</v>
+        <v>-3.986966955059721</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7732</v>
+        <v>7795</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>206.3824375138244</v>
+        <v>260.1748882880732</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>35.7</v>
+        <v>350</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>50.07747832598863</v>
+        <v>40.57028090749659</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.68531386969998</v>
+        <v>15.91417365897041</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1382437513824375</v>
+        <v>1.017488828807325</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0103886181428731</v>
+        <v>-4.896141820700795</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6873</v>
+        <v>7772</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>202.5823016950134</v>
+        <v>259.4707691677681</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>81.7</v>
+        <v>143.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.26365162470317</v>
+        <v>42.94647391981658</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.75943042446133</v>
+        <v>12.03314032284102</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.258230169501344</v>
+        <v>0.4470769167768164</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.7359890182751249</v>
+        <v>-0.8331683743306622</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6988</v>
+        <v>6887</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>199.3767884320156</v>
+        <v>258.5286480795857</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>13.85</v>
+        <v>34.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>31.32453625880325</v>
+        <v>48.8341554833431</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.42775695504188</v>
+        <v>8.373633619882309</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4376788432015544</v>
+        <v>0.8528648079585617</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2526970831735289</v>
+        <v>0.4621875730922389</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6967</v>
+        <v>6937</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>198.7311824588314</v>
+        <v>255.2749162841917</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>277.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45.04471955266869</v>
+        <v>43.17190039407148</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.42081593197756</v>
+        <v>16.42591594462982</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8731182458831404</v>
+        <v>0.5274916284191704</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1741091912184977</v>
+        <v>-4.490496844982484</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8034</v>
+        <v>6913</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>195.0346228360582</v>
+        <v>253.5134362939624</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>23.2</v>
+        <v>123</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.14977658341101</v>
+        <v>39.65472768910043</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.13700319346762</v>
+        <v>19.89815965906152</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5034622836058243</v>
+        <v>0.3513436293962333</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1113387103550276</v>
+        <v>-2.19337699052994</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6877</v>
+        <v>6919</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>193.9506990440987</v>
+        <v>250.7870057241497</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>131</v>
+        <v>88.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,49 +6435,49 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>31.8049425249087</v>
+        <v>34.28914239209634</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.64198416522114</v>
+        <v>14.80941900015333</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.39506990440987</v>
+        <v>0.5787005724149682</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M113" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-3.780922259991865</v>
+        <v>-0.9729398106350536</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6914</v>
+        <v>7791</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>192.1466538026898</v>
+        <v>243.1847080297952</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>141.5</v>
+        <v>62.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>44.31061153225159</v>
+        <v>37.71404687580581</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.17978506500853</v>
+        <v>27.45535361751498</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7146653802689822</v>
+        <v>0.3184708029795137</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1704556316069243</v>
+        <v>-0.364138067889481</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6962</v>
+        <v>7823</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>155.1304097007519</v>
+        <v>211.7741183831367</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>34.8</v>
+        <v>83.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.44523920058369</v>
+        <v>30.46071759679407</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.12843581610085</v>
+        <v>28.18039688687769</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5130409700751882</v>
+        <v>0.1774118383136683</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.5491461882843095</v>
+        <v>-2.479154100771361</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6969</v>
+        <v>8011</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>152.2720895065887</v>
+        <v>211.0069777515121</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>26.75</v>
+        <v>17.95</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>29.85494292883357</v>
+        <v>42.4139533512897</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20.28158136397677</v>
+        <v>18.50829996929248</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7272089506588728</v>
+        <v>0.600697775151208</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.081402633407717</v>
+        <v>0.0207903888710042</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6928</v>
+        <v>6971</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>146.6633092252471</v>
+        <v>205.8325093529007</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>43.05</v>
+        <v>26.65</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>33.68988759279067</v>
+        <v>35.55080935994161</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.11190221866517</v>
+        <v>15.06800795750079</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.166330922524707</v>
+        <v>0.58325093529007</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.419999200126545</v>
+        <v>0.009737940094108499</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7402</v>
+        <v>6873</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>137.6698533833618</v>
+        <v>202.8951104560917</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>91</v>
+        <v>81.7</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>30.53347203747802</v>
+        <v>38.26365167924639</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>19.3344261709993</v>
+        <v>14.7594304442297</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7669853383361768</v>
+        <v>1.289511045609166</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0099419092759411</v>
+        <v>-0.7359890189429075</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7770</v>
+        <v>6928</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>135.4296152876225</v>
+        <v>196.7064947779529</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>42</v>
+        <v>43.05</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.97519720611843</v>
+        <v>33.68988752341713</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7.181990135409208</v>
+        <v>18.11190225473951</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5429615287622469</v>
+        <v>1.170649477795295</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0428458965204382</v>
+        <v>-0.4199992001170028</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>8045</v>
+        <v>8034</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>135.1573599848794</v>
+        <v>195.0346228360582</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>61.6</v>
+        <v>23.2</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>37.86170746862568</v>
+        <v>39.14977653639809</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.95808517380953</v>
+        <v>16.13700314638124</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5157359984879427</v>
+        <v>0.5034622836058243</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.5907880897275875</v>
+        <v>-0.111338710364568</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6936</v>
+        <v>6877</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>134.3389030385338</v>
+        <v>193.9506990440987</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>33.2</v>
+        <v>131</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.90426944989631</v>
+        <v>31.80494249083686</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.53773922709356</v>
+        <v>19.64198413270184</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4338903038533798</v>
+        <v>1.39506990440987</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0334434391973211</v>
+        <v>-3.780922260030006</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6953</v>
+        <v>7402</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>133.6408489290258</v>
+        <v>137.6698533833618</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>216.5</v>
+        <v>91</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>32.99481686049707</v>
+        <v>30.53347197719259</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.09464663332618</v>
+        <v>19.33442613477355</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.364084892902582</v>
+        <v>0.7669853383361768</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-4.058924079428854</v>
+        <v>-0.009941909123305</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7547</v>
+        <v>7770</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>132.7728801199206</v>
+        <v>135.4296152876225</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>57.6</v>
+        <v>42</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>34.57075061249621</v>
+        <v>46.97519556469604</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>16.75823196012295</v>
+        <v>7.181990130944469</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.2772880119920593</v>
+        <v>0.5429615287622469</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.4733980051272231</v>
+        <v>0.0428458965204382</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6919</v>
+        <v>6953</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>125.6156652100849</v>
+        <v>133.6408489290258</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>88.2</v>
+        <v>216.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>34.28914396120678</v>
+        <v>32.99481683953918</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>14.80941893337506</v>
+        <v>19.09464667533926</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5615665210084932</v>
+        <v>1.364084892902582</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.9729398170828696</v>
+        <v>-4.058924079619626</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7703</v>
+        <v>7547</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>94.26060408799418</v>
+        <v>132.7728801199206</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>190</v>
+        <v>57.6</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>34.34810097195944</v>
+        <v>34.57075056151416</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>16.36664580952563</v>
+        <v>16.75823195165811</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4260604087994186</v>
+        <v>0.2772880119920593</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-1.89817665917665</v>
+        <v>-0.4733980050318114</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6887</v>
+        <v>8045</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>68.49442509111599</v>
+        <v>115.2439427228725</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>34.5</v>
+        <v>61.6</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>48.83415558240708</v>
+        <v>37.86170737275393</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>8.373632669971371</v>
+        <v>16.95808515449575</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.8494425091115981</v>
+        <v>0.5243942722872462</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.4621875721764207</v>
+        <v>-0.5907880897466726</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6971</v>
+        <v>7703</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>65.8325093529007</v>
+        <v>94.26060408799418</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>26.65</v>
+        <v>190</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>35.55080983249445</v>
+        <v>34.34810092476346</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>15.06800791380051</v>
+        <v>16.36664580952564</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.58325093529007</v>
+        <v>0.4260604087994186</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.009737939807915499</v>
+        <v>-1.898176658985842</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
